--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_MainPanelUI.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_MainPanelUI.xlsx
@@ -416,13 +416,13 @@
     <t>KLAppearGroupPanel</t>
   </si>
   <si>
-    <t>外观</t>
-  </si>
-  <si>
-    <t>外    观</t>
-  </si>
-  <si>
-    <t>btn_waiguan</t>
+    <t>称号</t>
+  </si>
+  <si>
+    <t>称    号</t>
+  </si>
+  <si>
+    <t>btn_chenghao</t>
   </si>
   <si>
     <t>dev/outui/AppearGroup/Panel/KLAppearGroup/KLAppearGroupPanel</t>
@@ -990,7 +990,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1151,11 +1151,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2612,7 +2607,7 @@
       <c r="B12" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D12" s="2" t="s">

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_MainPanelUI.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_MainPanelUI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_MainPanelUI" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_MainPanelUI!$G$1:$G$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_MainPanelUI!$G$1:$G$47</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="263">
   <si>
     <t>id</t>
   </si>
@@ -452,7 +452,7 @@
     <t>KLAttrPanel</t>
   </si>
   <si>
-    <t>角色_加点</t>
+    <t>角色加点</t>
   </si>
   <si>
     <t>角色</t>
@@ -978,6 +978,18 @@
   </si>
   <si>
     <t>BtnKaLiMa</t>
+  </si>
+  <si>
+    <t>KLArchangelGrailPanel</t>
+  </si>
+  <si>
+    <t>圣杯</t>
+  </si>
+  <si>
+    <t>btn_angel_equip</t>
+  </si>
+  <si>
+    <t>dev/outui/Archangel/Panel/KLArchangelGroup/KLArchangelGroupPanel</t>
   </si>
 </sst>
 </file>
@@ -2151,7 +2163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2407,6 +2419,9 @@
         <v>52</v>
       </c>
       <c r="G6" s="4">
+        <v>3</v>
+      </c>
+      <c r="H6" s="1">
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -2658,7 +2673,10 @@
         <v>97</v>
       </c>
       <c r="G13" s="1">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H13" s="1">
+        <v>2</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>46</v>
@@ -2677,7 +2695,7 @@
       <c r="B14" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>101</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -2690,6 +2708,9 @@
         <v>103</v>
       </c>
       <c r="G14" s="1">
+        <v>3</v>
+      </c>
+      <c r="H14" s="1">
         <v>1</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -2777,7 +2798,7 @@
         <v>120</v>
       </c>
       <c r="G17" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" s="1">
         <v>11</v>
@@ -2874,7 +2895,7 @@
         <v>135</v>
       </c>
       <c r="G20" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1">
@@ -3076,13 +3097,13 @@
         <v>164</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H26" s="1">
         <v>1</v>
       </c>
       <c r="I26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>165</v>
@@ -3465,7 +3486,7 @@
         <v>225</v>
       </c>
       <c r="G39" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39" s="1">
         <v>6</v>
@@ -3529,7 +3550,7 @@
         <v>235</v>
       </c>
       <c r="G41" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H41" s="1">
         <v>2</v>
@@ -3654,7 +3675,7 @@
         <v>252</v>
       </c>
       <c r="G45" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H45" s="1">
         <v>3</v>
@@ -3686,7 +3707,7 @@
         <v>256</v>
       </c>
       <c r="G46" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" s="1">
         <v>10</v>
@@ -3701,8 +3722,40 @@
         <v>258</v>
       </c>
     </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="1">
+        <v>241</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G47" s="1">
+        <v>3</v>
+      </c>
+      <c r="H47" s="1">
+        <v>3</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="G1:G46" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="G1:G47" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
